--- a/docs/downloads/04/tbl_cm_r_sex_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_cm_r_sex_alaotra_ambatoharanana.xlsx
@@ -387,12 +387,6 @@
           <t>Femme</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
